--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121141552</v>
       </c>
       <c r="B3" t="n">
-        <v>44819</v>
+        <v>44822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>121141551</v>
       </c>
       <c r="B4" t="n">
-        <v>44819</v>
+        <v>44822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121141552</v>
+        <v>121141551</v>
       </c>
       <c r="B3" t="n">
         <v>44822</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667559</v>
+        <v>667539</v>
       </c>
       <c r="R3" t="n">
-        <v>6615479</v>
+        <v>6615669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121141551</v>
+        <v>121141552</v>
       </c>
       <c r="B4" t="n">
         <v>44822</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667539</v>
+        <v>667559</v>
       </c>
       <c r="R4" t="n">
-        <v>6615669</v>
+        <v>6615479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121141551</v>
+        <v>121141552</v>
       </c>
       <c r="B3" t="n">
-        <v>44822</v>
+        <v>44825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667539</v>
+        <v>667559</v>
       </c>
       <c r="R3" t="n">
-        <v>6615669</v>
+        <v>6615479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121141552</v>
+        <v>121141551</v>
       </c>
       <c r="B4" t="n">
-        <v>44822</v>
+        <v>44825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667559</v>
+        <v>667539</v>
       </c>
       <c r="R4" t="n">
-        <v>6615479</v>
+        <v>6615669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114392035</v>
+        <v>114392037</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667528</v>
+        <v>667541</v>
       </c>
       <c r="R2" t="n">
-        <v>6615281</v>
+        <v>6615651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +781,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121141552</v>
+        <v>114391758</v>
       </c>
       <c r="B3" t="n">
-        <v>44825</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208307</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667559</v>
+        <v>667834</v>
       </c>
       <c r="R3" t="n">
-        <v>6615479</v>
+        <v>6614975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,26 +876,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
+          <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121141551</v>
+        <v>114392035</v>
       </c>
       <c r="B4" t="n">
-        <v>44825</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,31 +898,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208307</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667539</v>
+        <v>667528</v>
       </c>
       <c r="R4" t="n">
-        <v>6615669</v>
+        <v>6615281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +982,450 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ASC0006 Arlanda Fågelinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114445142</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>667499</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ASC0006 Arlanda Fågelinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121141550</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45297</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667527</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6615717</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Flor Rhebergen</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121141551</v>
+      </c>
+      <c r="B7" t="n">
+        <v>45297</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6615669</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121141552</v>
+      </c>
+      <c r="B8" t="n">
+        <v>45297</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667559</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6615479</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
         </is>

--- a/artfynd/A 64357-2023 artfynd.xlsx
+++ b/artfynd/A 64357-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114392037</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114391758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114392035</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114445142</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
           <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121141550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
           <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121141551</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,8 +1465,22 @@
           <t>ASC0019_J_KBN0027_Trollsländor_2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121141552</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>